--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9164,0.0695,0.0119,0.0015</t>
-  </si>
-  <si>
-    <t>0.9184,0.0381,0.0109,0.0064</t>
-  </si>
-  <si>
-    <t>0.9442,0.0360,0.0078,0.0015</t>
-  </si>
-  <si>
-    <t>0.9797,0.0075,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.9513,0.0515,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9184,0.0705,0.0039,0.0025</t>
-  </si>
-  <si>
-    <t>0.8070,0.2207,0.0061,0.0014</t>
-  </si>
-  <si>
-    <t>0.9411,0.0619,0.0018,0.0011</t>
-  </si>
-  <si>
-    <t>0.9624,0.0376,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9134,0.1076,0.0020,0.0009</t>
-  </si>
-  <si>
-    <t>0.9408,0.0503,0.0023,0.0016</t>
-  </si>
-  <si>
-    <t>0.8738,0.1841,0.0034,0.0009</t>
-  </si>
-  <si>
-    <t>0.9820,0.0071,0.0076,0.0001</t>
-  </si>
-  <si>
-    <t>0.7215,0.0511,0.3103,0.0070</t>
-  </si>
-  <si>
-    <t>0.9721,0.0099,0.0142,0.0002</t>
-  </si>
-  <si>
-    <t>0.6702,0.0169,0.4420,0.0117</t>
-  </si>
-  <si>
-    <t>0.7957,0.2009,0.0269,0.0007</t>
-  </si>
-  <si>
-    <t>0.2192,0.8837,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9286,0.1085,0.0040,0.0002</t>
-  </si>
-  <si>
-    <t>0.9237,0.1204,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.7489,0.4345,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.2715,0.8526,0.0064,0.0003</t>
-  </si>
-  <si>
-    <t>0.9880,0.0012,0.0129,0.0002</t>
-  </si>
-  <si>
-    <t>0.9572,0.0200,0.0178,0.0014</t>
-  </si>
-  <si>
-    <t>0.5123,0.0234,0.4972,0.0011</t>
-  </si>
-  <si>
-    <t>0.9697,0.0041,0.0390,0.0008</t>
-  </si>
-  <si>
-    <t>0.9898,0.0017,0.0081,0.0002</t>
-  </si>
-  <si>
-    <t>0.9670,0.0036,0.0487,0.0003</t>
-  </si>
-  <si>
-    <t>0.7871,0.0071,0.3439,0.0015</t>
-  </si>
-  <si>
-    <t>0.9616,0.0399,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.9444,0.0639,0.0040,0.0005</t>
-  </si>
-  <si>
-    <t>0.0620,0.1048,0.9464,0.0008</t>
-  </si>
-  <si>
-    <t>0.5006,0.4793,0.0471,0.0009</t>
-  </si>
-  <si>
-    <t>0.9402,0.0606,0.0044,0.0007</t>
-  </si>
-  <si>
-    <t>0.9305,0.0531,0.0163,0.0014</t>
-  </si>
-  <si>
-    <t>0.9772,0.0298,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9751,0.0169,0.0035,0.0004</t>
-  </si>
-  <si>
-    <t>0.3132,0.2069,0.3050,0.0002</t>
-  </si>
-  <si>
-    <t>0.9886,0.0018,0.0091,0.0001</t>
-  </si>
-  <si>
-    <t>0.9864,0.0012,0.0192,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0001,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.9036,0.0070,0.1997,0.0007</t>
-  </si>
-  <si>
-    <t>0.6361,0.0493,0.1335,0.0001</t>
-  </si>
-  <si>
-    <t>0.9694,0.0057,0.0288,0.0003</t>
-  </si>
-  <si>
-    <t>0.9718,0.0166,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.9793,0.0157,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9878,0.0099,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9796,0.0177,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0958,0.0742,0.8767,0.0008</t>
-  </si>
-  <si>
-    <t>0.0752,0.0275,0.9384,0.0006</t>
-  </si>
-  <si>
-    <t>0.9425,0.0019,0.1197,0.0002</t>
-  </si>
-  <si>
-    <t>0.9640,0.0022,0.0643,0.0006</t>
-  </si>
-  <si>
-    <t>0.0719,0.0053,0.9410,0.0013</t>
-  </si>
-  <si>
-    <t>0.9633,0.0049,0.0489,0.0002</t>
-  </si>
-  <si>
-    <t>0.9034,0.1091,0.0058,0.0015</t>
-  </si>
-  <si>
-    <t>0.9568,0.0273,0.0017,0.0021</t>
-  </si>
-  <si>
-    <t>0.9093,0.1180,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.5978,0.1133,0.3365,0.0035</t>
-  </si>
-  <si>
-    <t>0.9505,0.0444,0.0021,0.0011</t>
-  </si>
-  <si>
-    <t>0.7929,0.2708,0.0067,0.0009</t>
-  </si>
-  <si>
-    <t>0.9258,0.0858,0.0019,0.0009</t>
-  </si>
-  <si>
-    <t>0.2711,0.0497,0.8138,0.0003</t>
-  </si>
-  <si>
-    <t>0.7217,0.0112,0.4438,0.0006</t>
-  </si>
-  <si>
-    <t>0.4570,0.0625,0.5127,0.0021</t>
-  </si>
-  <si>
-    <t>0.2798,0.2529,0.4443,0.0005</t>
-  </si>
-  <si>
-    <t>0.1164,0.0030,0.9479,0.0003</t>
-  </si>
-  <si>
-    <t>0.7996,0.2266,0.0088,0.0001</t>
-  </si>
-  <si>
-    <t>0.2158,0.8622,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.8565,0.1070,0.0568,0.0031</t>
-  </si>
-  <si>
-    <t>0.9600,0.0563,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0494,0.0942,0.9576,0.0004</t>
-  </si>
-  <si>
-    <t>0.1954,0.5603,0.2367,0.0005</t>
-  </si>
-  <si>
-    <t>0.9052,0.0130,0.1349,0.0010</t>
-  </si>
-  <si>
-    <t>0.3424,0.4612,0.0632,0.0002</t>
-  </si>
-  <si>
-    <t>0.6250,0.0573,0.2503,0.0004</t>
-  </si>
-  <si>
-    <t>0.8885,0.0646,0.0329,0.0052</t>
-  </si>
-  <si>
-    <t>0.9381,0.0125,0.0027,0.0138</t>
-  </si>
-  <si>
-    <t>0.9753,0.0109,0.0019,0.0015</t>
-  </si>
-  <si>
-    <t>0.9527,0.0126,0.0026,0.0058</t>
-  </si>
-  <si>
-    <t>0.9694,0.0064,0.0053,0.0062</t>
-  </si>
-  <si>
-    <t>0.9537,0.0149,0.0055,0.0064</t>
-  </si>
-  <si>
-    <t>0.4739,0.3101,0.0874,0.0001</t>
-  </si>
-  <si>
-    <t>0.7364,0.0074,0.3755,0.0007</t>
-  </si>
-  <si>
-    <t>0.9058,0.0028,0.1890,0.0001</t>
-  </si>
-  <si>
-    <t>0.8674,0.0077,0.2007,0.0006</t>
-  </si>
-  <si>
-    <t>0.8057,0.1300,0.0207,0.0001</t>
-  </si>
-  <si>
-    <t>0.8605,0.0902,0.0213,0.0001</t>
-  </si>
-  <si>
-    <t>0.9360,0.0599,0.0038,0.0011</t>
-  </si>
-  <si>
-    <t>0.9696,0.0223,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.9136,0.0995,0.0035,0.0010</t>
-  </si>
-  <si>
-    <t>0.9439,0.0577,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9692,0.0272,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9102,0.0865,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.9382,0.0602,0.0021,0.0009</t>
-  </si>
-  <si>
-    <t>0.9771,0.0198,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9591,0.0330,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9690,0.0270,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9218,0.0773,0.0025,0.0012</t>
-  </si>
-  <si>
-    <t>0.9715,0.0185,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9848,0.0133,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.8149,0.1937,0.0080,0.0024</t>
-  </si>
-  <si>
-    <t>0.9713,0.0199,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.8940,0.1223,0.0091,0.0018</t>
-  </si>
-  <si>
-    <t>0.0700,0.0930,0.9381,0.0034</t>
-  </si>
-  <si>
-    <t>0.8769,0.0026,0.2787,0.0002</t>
-  </si>
-  <si>
-    <t>0.9946,0.0006,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.9514,0.0028,0.0910,0.0004</t>
-  </si>
-  <si>
-    <t>0.1902,0.9004,0.0048,0.0007</t>
-  </si>
-  <si>
-    <t>0.3537,0.7549,0.0106,0.0008</t>
-  </si>
-  <si>
-    <t>0.3741,0.7761,0.0096,0.0006</t>
-  </si>
-  <si>
-    <t>0.8992,0.1540,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.6728,0.4510,0.0073,0.0004</t>
-  </si>
-  <si>
-    <t>0.3797,0.7767,0.0051,0.0005</t>
-  </si>
-  <si>
-    <t>0.6329,0.4973,0.0102,0.0014</t>
-  </si>
-  <si>
-    <t>0.9638,0.0137,0.0192,0.0009</t>
-  </si>
-  <si>
-    <t>0.8454,0.0139,0.2512,0.0019</t>
-  </si>
-  <si>
-    <t>0.9637,0.0125,0.0130,0.0004</t>
-  </si>
-  <si>
-    <t>0.9544,0.0244,0.0197,0.0008</t>
-  </si>
-  <si>
-    <t>0.8981,0.1115,0.0111,0.0014</t>
-  </si>
-  <si>
-    <t>0.6783,0.5285,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.6574,0.4696,0.0062,0.0003</t>
-  </si>
-  <si>
-    <t>0.9176,0.1310,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.1809,0.3456,0.0734,0.0000</t>
-  </si>
-  <si>
-    <t>0.9643,0.0447,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9529,0.0502,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9021,0.1366,0.0070,0.0007</t>
-  </si>
-  <si>
-    <t>0.9593,0.0358,0.0048,0.0010</t>
-  </si>
-  <si>
-    <t>0.8841,0.1340,0.0066,0.0013</t>
-  </si>
-  <si>
-    <t>0.9450,0.0425,0.0029,0.0013</t>
-  </si>
-  <si>
-    <t>0.8829,0.1476,0.0055,0.0009</t>
-  </si>
-  <si>
-    <t>0.8916,0.1211,0.0035,0.0010</t>
-  </si>
-  <si>
-    <t>0.9487,0.0502,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.6028,0.4737,0.0233,0.0037</t>
-  </si>
-  <si>
-    <t>0.7879,0.2848,0.0093,0.0021</t>
-  </si>
-  <si>
-    <t>0.9085,0.0180,0.1085,0.0010</t>
-  </si>
-  <si>
-    <t>0.8404,0.0032,0.3083,0.0008</t>
-  </si>
-  <si>
-    <t>0.9312,0.0013,0.1854,0.0003</t>
-  </si>
-  <si>
-    <t>0.9493,0.0011,0.1270,0.0003</t>
-  </si>
-  <si>
-    <t>0.9796,0.0073,0.0093,0.0004</t>
-  </si>
-  <si>
-    <t>0.9601,0.0050,0.0385,0.0005</t>
-  </si>
-  <si>
-    <t>0.9348,0.0305,0.0240,0.0007</t>
-  </si>
-  <si>
-    <t>0.9821,0.0081,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.9756,0.0088,0.0057,0.0011</t>
-  </si>
-  <si>
-    <t>0.9505,0.0046,0.0035,0.0182</t>
-  </si>
-  <si>
-    <t>0.8736,0.0157,0.0407,0.0319</t>
-  </si>
-  <si>
-    <t>0.9662,0.0068,0.0045,0.0042</t>
-  </si>
-  <si>
-    <t>0.1561,0.8438,0.0105,0.0000</t>
-  </si>
-  <si>
-    <t>0.9632,0.0260,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.9648,0.0322,0.0018,0.0007</t>
-  </si>
-  <si>
-    <t>0.9792,0.0191,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.7280,0.3082,0.0078,0.0014</t>
-  </si>
-  <si>
-    <t>0.9166,0.0876,0.0054,0.0011</t>
-  </si>
-  <si>
-    <t>0.9728,0.0158,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.7626,0.2362,0.0427,0.0060</t>
-  </si>
-  <si>
-    <t>0.7576,0.0087,0.3180,0.0174</t>
-  </si>
-  <si>
-    <t>0.9187,0.0739,0.0067,0.0015</t>
-  </si>
-  <si>
-    <t>0.8602,0.1196,0.0149,0.0048</t>
-  </si>
-  <si>
-    <t>0.9192,0.1108,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.9757,0.0139,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9746,0.0294,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.7707,0.2727,0.0159,0.0013</t>
-  </si>
-  <si>
-    <t>0.9146,0.1231,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.9271,0.0811,0.0058,0.0003</t>
-  </si>
-  <si>
-    <t>0.9065,0.1054,0.0039,0.0011</t>
-  </si>
-  <si>
-    <t>0.8775,0.1760,0.0028,0.0012</t>
-  </si>
-  <si>
-    <t>0.8953,0.0961,0.0116,0.0029</t>
-  </si>
-  <si>
-    <t>0.8172,0.2120,0.0052,0.0022</t>
-  </si>
-  <si>
-    <t>0.9025,0.0822,0.0059,0.0029</t>
-  </si>
-  <si>
-    <t>0.9006,0.0865,0.0121,0.0026</t>
-  </si>
-  <si>
-    <t>0.9392,0.0736,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.7794,0.2264,0.0039,0.0027</t>
-  </si>
-  <si>
-    <t>0.9116,0.0863,0.0041,0.0013</t>
-  </si>
-  <si>
-    <t>0.7921,0.3022,0.0104,0.0005</t>
-  </si>
-  <si>
-    <t>0.9024,0.1369,0.0031,0.0005</t>
-  </si>
-  <si>
-    <t>0.8950,0.1188,0.0092,0.0009</t>
-  </si>
-  <si>
-    <t>0.8479,0.1991,0.0045,0.0011</t>
-  </si>
-  <si>
-    <t>0.9709,0.0183,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.9750,0.0232,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9188,0.0818,0.0063,0.0008</t>
-  </si>
-  <si>
-    <t>0.6242,0.0646,0.4237,0.0010</t>
-  </si>
-  <si>
-    <t>0.9839,0.0116,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.0499,0.0265,0.9111,0.0007</t>
-  </si>
-  <si>
-    <t>0.8590,0.0124,0.1860,0.0009</t>
-  </si>
-  <si>
-    <t>0.6179,0.0658,0.3433,0.0014</t>
-  </si>
-  <si>
-    <t>0.3985,0.2443,0.2474,0.0007</t>
-  </si>
-  <si>
-    <t>0.9534,0.0039,0.0609,0.0003</t>
-  </si>
-  <si>
-    <t>0.8707,0.0036,0.2566,0.0007</t>
-  </si>
-  <si>
-    <t>0.9114,0.0067,0.1272,0.0007</t>
-  </si>
-  <si>
-    <t>0.8991,0.0453,0.0445,0.0009</t>
-  </si>
-  <si>
-    <t>0.9623,0.0161,0.0137,0.0006</t>
-  </si>
-  <si>
-    <t>0.9917,0.0017,0.0031,0.0003</t>
-  </si>
-  <si>
-    <t>0.9762,0.0122,0.0053,0.0002</t>
-  </si>
-  <si>
-    <t>0.9344,0.0403,0.0141,0.0004</t>
-  </si>
-  <si>
-    <t>0.9656,0.0161,0.0094,0.0004</t>
-  </si>
-  <si>
-    <t>0.9411,0.0204,0.0298,0.0011</t>
-  </si>
-  <si>
-    <t>0.9068,0.0291,0.0562,0.0008</t>
-  </si>
-  <si>
-    <t>0.8231,0.3163,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.7151,0.5193,0.0025,0.0003</t>
-  </si>
-  <si>
-    <t>0.8948,0.1074,0.0066,0.0016</t>
-  </si>
-  <si>
-    <t>0.8684,0.1887,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.7382,0.3564,0.0126,0.0015</t>
-  </si>
-  <si>
-    <t>0.9782,0.0109,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.9469,0.0372,0.0110,0.0003</t>
-  </si>
-  <si>
-    <t>0.9560,0.0304,0.0057,0.0003</t>
-  </si>
-  <si>
-    <t>0.9242,0.0273,0.0519,0.0011</t>
-  </si>
-  <si>
-    <t>0.9610,0.0124,0.0196,0.0022</t>
-  </si>
-  <si>
-    <t>0.0237,0.5372,0.7827,0.0010</t>
-  </si>
-  <si>
-    <t>0.9488,0.0046,0.0920,0.0012</t>
-  </si>
-  <si>
-    <t>0.9801,0.0035,0.0147,0.0002</t>
-  </si>
-  <si>
-    <t>0.9838,0.0007,0.0365,0.0001</t>
-  </si>
-  <si>
-    <t>0.9886,0.0019,0.0077,0.0000</t>
-  </si>
-  <si>
-    <t>0.9730,0.0153,0.0016,0.0013</t>
-  </si>
-  <si>
-    <t>0.9548,0.0441,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9601,0.0265,0.0026,0.0018</t>
-  </si>
-  <si>
-    <t>0.9515,0.0570,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9624,0.0445,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9058,0.1145,0.0022,0.0009</t>
-  </si>
-  <si>
-    <t>0.9148,0.1157,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.7888,0.2723,0.0138,0.0020</t>
-  </si>
-  <si>
-    <t>0.9791,0.0086,0.0065,0.0003</t>
-  </si>
-  <si>
-    <t>0.9347,0.0551,0.0104,0.0008</t>
-  </si>
-  <si>
-    <t>0.7570,0.2680,0.0236,0.0021</t>
-  </si>
-  <si>
-    <t>0.7526,0.0356,0.2308,0.0011</t>
-  </si>
-  <si>
-    <t>0.0979,0.1052,0.8182,0.0003</t>
-  </si>
-  <si>
-    <t>0.1773,0.1489,0.7774,0.0013</t>
-  </si>
-  <si>
-    <t>0.0261,0.0024,0.9899,0.0001</t>
-  </si>
-  <si>
-    <t>0.9626,0.0049,0.0651,0.0007</t>
-  </si>
-  <si>
-    <t>0.0950,0.0775,0.8356,0.0043</t>
-  </si>
-  <si>
-    <t>0.9847,0.0010,0.0248,0.0002</t>
-  </si>
-  <si>
-    <t>0.7609,0.0798,0.2183,0.0043</t>
-  </si>
-  <si>
-    <t>0.9583,0.0153,0.0110,0.0008</t>
-  </si>
-  <si>
-    <t>0.9796,0.0015,0.0272,0.0003</t>
-  </si>
-  <si>
-    <t>0.9863,0.0039,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.9481,0.0442,0.0016,0.0016</t>
-  </si>
-  <si>
-    <t>0.8854,0.1012,0.0035,0.0017</t>
-  </si>
-  <si>
-    <t>0.9732,0.0292,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.8054,0.2125,0.0048,0.0023</t>
-  </si>
-  <si>
-    <t>0.9643,0.0245,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.9229,0.0798,0.0033,0.0013</t>
-  </si>
-  <si>
-    <t>0.9453,0.0550,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.9259,0.0905,0.0026,0.0010</t>
-  </si>
-  <si>
-    <t>0.9806,0.0036,0.0201,0.0001</t>
-  </si>
-  <si>
-    <t>0.5647,0.0035,0.6757,0.0006</t>
-  </si>
-  <si>
-    <t>0.0962,0.0048,0.9480,0.0003</t>
-  </si>
-  <si>
-    <t>0.9738,0.0092,0.0079,0.0001</t>
-  </si>
-  <si>
-    <t>0.6117,0.0319,0.4498,0.0020</t>
-  </si>
-  <si>
-    <t>0.9361,0.0112,0.0608,0.0025</t>
-  </si>
-  <si>
-    <t>0.9950,0.0005,0.0050,0.0001</t>
-  </si>
-  <si>
-    <t>0.9558,0.0011,0.0816,0.0006</t>
-  </si>
-  <si>
-    <t>0.8950,0.0580,0.0187,0.0029</t>
-  </si>
-  <si>
-    <t>0.9723,0.0058,0.0117,0.0016</t>
-  </si>
-  <si>
-    <t>0.9826,0.0031,0.0025,0.0026</t>
-  </si>
-  <si>
-    <t>0.9465,0.0104,0.0070,0.0146</t>
-  </si>
-  <si>
-    <t>0.8918,0.0130,0.0628,0.0199</t>
-  </si>
-  <si>
-    <t>0.8890,0.1170,0.0097,0.0012</t>
+    <t>0.9672,0.0207,0.0067,0.0008</t>
+  </si>
+  <si>
+    <t>0.8876,0.0480,0.0340,0.0118</t>
+  </si>
+  <si>
+    <t>0.9710,0.0207,0.0033,0.0007</t>
+  </si>
+  <si>
+    <t>0.9702,0.0125,0.0018,0.0016</t>
+  </si>
+  <si>
+    <t>0.9853,0.0087,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9556,0.0364,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.8497,0.1237,0.0051,0.0028</t>
+  </si>
+  <si>
+    <t>0.8908,0.1069,0.0072,0.0028</t>
+  </si>
+  <si>
+    <t>0.9795,0.0183,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9643,0.0169,0.0012,0.0022</t>
+  </si>
+  <si>
+    <t>0.9521,0.0349,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.9184,0.1002,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9688,0.0129,0.0144,0.0004</t>
+  </si>
+  <si>
+    <t>0.9170,0.0399,0.0259,0.0006</t>
+  </si>
+  <si>
+    <t>0.9648,0.0159,0.0098,0.0002</t>
+  </si>
+  <si>
+    <t>0.6659,0.0393,0.3916,0.0034</t>
+  </si>
+  <si>
+    <t>0.9283,0.0886,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.6430,0.5136,0.0062,0.0002</t>
+  </si>
+  <si>
+    <t>0.6471,0.4641,0.0079,0.0004</t>
+  </si>
+  <si>
+    <t>0.8335,0.2431,0.0055,0.0004</t>
+  </si>
+  <si>
+    <t>0.2095,0.8719,0.0054,0.0008</t>
+  </si>
+  <si>
+    <t>0.4744,0.6785,0.0065,0.0007</t>
+  </si>
+  <si>
+    <t>0.9020,0.0194,0.1004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9806,0.0009,0.0348,0.0002</t>
+  </si>
+  <si>
+    <t>0.9246,0.0071,0.1032,0.0005</t>
+  </si>
+  <si>
+    <t>0.9808,0.0028,0.0227,0.0001</t>
+  </si>
+  <si>
+    <t>0.9736,0.0038,0.0273,0.0007</t>
+  </si>
+  <si>
+    <t>0.9836,0.0015,0.0194,0.0003</t>
+  </si>
+  <si>
+    <t>0.5919,0.0042,0.6033,0.0016</t>
+  </si>
+  <si>
+    <t>0.7581,0.4499,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9234,0.0573,0.0196,0.0008</t>
+  </si>
+  <si>
+    <t>0.0723,0.0413,0.9334,0.0025</t>
+  </si>
+  <si>
+    <t>0.5474,0.4169,0.0268,0.0002</t>
+  </si>
+  <si>
+    <t>0.9858,0.0078,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9614,0.0412,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.9644,0.0476,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9780,0.0245,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.4685,0.0878,0.3558,0.0026</t>
+  </si>
+  <si>
+    <t>0.9590,0.0021,0.0828,0.0009</t>
+  </si>
+  <si>
+    <t>0.9837,0.0017,0.0223,0.0001</t>
+  </si>
+  <si>
+    <t>0.9902,0.0015,0.0099,0.0002</t>
+  </si>
+  <si>
+    <t>0.8987,0.0016,0.2515,0.0002</t>
+  </si>
+  <si>
+    <t>0.2020,0.0140,0.7223,0.0027</t>
+  </si>
+  <si>
+    <t>0.8363,0.0009,0.3741,0.0002</t>
+  </si>
+  <si>
+    <t>0.9012,0.0943,0.0068,0.0009</t>
+  </si>
+  <si>
+    <t>0.6763,0.4804,0.0029,0.0000</t>
+  </si>
+  <si>
+    <t>0.9527,0.0366,0.0062,0.0001</t>
+  </si>
+  <si>
+    <t>0.9546,0.0368,0.0053,0.0000</t>
+  </si>
+  <si>
+    <t>0.1825,0.0517,0.8166,0.0064</t>
+  </si>
+  <si>
+    <t>0.5288,0.0152,0.5441,0.0002</t>
+  </si>
+  <si>
+    <t>0.9048,0.0204,0.0995,0.0016</t>
+  </si>
+  <si>
+    <t>0.9792,0.0035,0.0179,0.0003</t>
+  </si>
+  <si>
+    <t>0.0557,0.0151,0.9044,0.0015</t>
+  </si>
+  <si>
+    <t>0.6486,0.0212,0.3344,0.0007</t>
+  </si>
+  <si>
+    <t>0.9220,0.0858,0.0034,0.0011</t>
+  </si>
+  <si>
+    <t>0.9203,0.0607,0.0071,0.0022</t>
+  </si>
+  <si>
+    <t>0.9705,0.0126,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.0128,0.8709,0.8452,0.0008</t>
+  </si>
+  <si>
+    <t>0.8646,0.1603,0.0078,0.0012</t>
+  </si>
+  <si>
+    <t>0.9777,0.0127,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.8694,0.1716,0.0074,0.0013</t>
+  </si>
+  <si>
+    <t>0.0527,0.0245,0.9615,0.0008</t>
+  </si>
+  <si>
+    <t>0.1443,0.0012,0.9525,0.0002</t>
+  </si>
+  <si>
+    <t>0.9737,0.0016,0.0572,0.0002</t>
+  </si>
+  <si>
+    <t>0.3211,0.5560,0.0653,0.0001</t>
+  </si>
+  <si>
+    <t>0.0981,0.0099,0.9521,0.0004</t>
+  </si>
+  <si>
+    <t>0.7369,0.3439,0.0097,0.0002</t>
+  </si>
+  <si>
+    <t>0.5428,0.6959,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9240,0.0961,0.0058,0.0005</t>
+  </si>
+  <si>
+    <t>0.9647,0.0301,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.1715,0.2127,0.8273,0.0043</t>
+  </si>
+  <si>
+    <t>0.6458,0.0516,0.4462,0.0010</t>
+  </si>
+  <si>
+    <t>0.9069,0.0318,0.0618,0.0003</t>
+  </si>
+  <si>
+    <t>0.2877,0.5705,0.0596,0.0001</t>
+  </si>
+  <si>
+    <t>0.5226,0.2319,0.1230,0.0005</t>
+  </si>
+  <si>
+    <t>0.9524,0.0149,0.0164,0.0048</t>
+  </si>
+  <si>
+    <t>0.9293,0.0173,0.0097,0.0122</t>
+  </si>
+  <si>
+    <t>0.9894,0.0033,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9736,0.0098,0.0025,0.0025</t>
+  </si>
+  <si>
+    <t>0.9583,0.0160,0.0084,0.0031</t>
+  </si>
+  <si>
+    <t>0.9626,0.0097,0.0117,0.0045</t>
+  </si>
+  <si>
+    <t>0.9288,0.0256,0.0458,0.0006</t>
+  </si>
+  <si>
+    <t>0.9521,0.0134,0.0430,0.0002</t>
+  </si>
+  <si>
+    <t>0.6172,0.0142,0.3994,0.0004</t>
+  </si>
+  <si>
+    <t>0.3325,0.0070,0.8211,0.0003</t>
+  </si>
+  <si>
+    <t>0.7183,0.0801,0.0859,0.0004</t>
+  </si>
+  <si>
+    <t>0.9881,0.0020,0.0081,0.0001</t>
+  </si>
+  <si>
+    <t>0.9726,0.0213,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9409,0.0721,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9234,0.1020,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.9443,0.0511,0.0018,0.0011</t>
+  </si>
+  <si>
+    <t>0.9116,0.0879,0.0042,0.0015</t>
+  </si>
+  <si>
+    <t>0.9449,0.0381,0.0031,0.0016</t>
+  </si>
+  <si>
+    <t>0.9312,0.0691,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.8507,0.2012,0.0048,0.0010</t>
+  </si>
+  <si>
+    <t>0.9510,0.0300,0.0014,0.0017</t>
+  </si>
+  <si>
+    <t>0.9595,0.0287,0.0023,0.0010</t>
+  </si>
+  <si>
+    <t>0.9568,0.0322,0.0041,0.0013</t>
+  </si>
+  <si>
+    <t>0.9862,0.0074,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.8678,0.1810,0.0044,0.0010</t>
+  </si>
+  <si>
+    <t>0.9711,0.0218,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9426,0.0649,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9595,0.0308,0.0025,0.0017</t>
+  </si>
+  <si>
+    <t>0.0724,0.0090,0.9632,0.0005</t>
+  </si>
+  <si>
+    <t>0.9772,0.0029,0.0354,0.0004</t>
+  </si>
+  <si>
+    <t>0.9604,0.0168,0.0101,0.0017</t>
+  </si>
+  <si>
+    <t>0.5757,0.0648,0.2646,0.0006</t>
+  </si>
+  <si>
+    <t>0.6468,0.5508,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.5855,0.5114,0.0136,0.0017</t>
+  </si>
+  <si>
+    <t>0.7362,0.3547,0.0120,0.0006</t>
+  </si>
+  <si>
+    <t>0.9011,0.1326,0.0036,0.0008</t>
+  </si>
+  <si>
+    <t>0.0813,0.9387,0.0097,0.0003</t>
+  </si>
+  <si>
+    <t>0.1316,0.9194,0.0054,0.0002</t>
+  </si>
+  <si>
+    <t>0.8750,0.1706,0.0034,0.0007</t>
+  </si>
+  <si>
+    <t>0.9191,0.0717,0.0117,0.0004</t>
+  </si>
+  <si>
+    <t>0.9544,0.0077,0.0635,0.0004</t>
+  </si>
+  <si>
+    <t>0.9738,0.0123,0.0083,0.0004</t>
+  </si>
+  <si>
+    <t>0.9638,0.0235,0.0088,0.0002</t>
+  </si>
+  <si>
+    <t>0.8372,0.1319,0.0248,0.0039</t>
+  </si>
+  <si>
+    <t>0.8932,0.1212,0.0060,0.0000</t>
+  </si>
+  <si>
+    <t>0.9492,0.0518,0.0037,0.0000</t>
+  </si>
+  <si>
+    <t>0.9472,0.0561,0.0062,0.0003</t>
+  </si>
+  <si>
+    <t>0.2825,0.1529,0.3061,0.0004</t>
+  </si>
+  <si>
+    <t>0.9627,0.0434,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.8496,0.1421,0.0210,0.0011</t>
+  </si>
+  <si>
+    <t>0.8445,0.1888,0.0088,0.0015</t>
+  </si>
+  <si>
+    <t>0.9194,0.0787,0.0034,0.0009</t>
+  </si>
+  <si>
+    <t>0.9431,0.0804,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.9502,0.0564,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.8778,0.0983,0.0129,0.0028</t>
+  </si>
+  <si>
+    <t>0.8191,0.2665,0.0057,0.0009</t>
+  </si>
+  <si>
+    <t>0.9795,0.0128,0.0025,0.0008</t>
+  </si>
+  <si>
+    <t>0.8384,0.1789,0.0119,0.0023</t>
+  </si>
+  <si>
+    <t>0.8932,0.1258,0.0034,0.0006</t>
+  </si>
+  <si>
+    <t>0.8516,0.0133,0.2139,0.0008</t>
+  </si>
+  <si>
+    <t>0.8777,0.0099,0.1514,0.0004</t>
+  </si>
+  <si>
+    <t>0.9170,0.0063,0.1475,0.0003</t>
+  </si>
+  <si>
+    <t>0.9914,0.0005,0.0120,0.0001</t>
+  </si>
+  <si>
+    <t>0.9918,0.0024,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.9907,0.0037,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9630,0.0180,0.0119,0.0004</t>
+  </si>
+  <si>
+    <t>0.9737,0.0146,0.0046,0.0005</t>
+  </si>
+  <si>
+    <t>0.9753,0.0072,0.0041,0.0022</t>
+  </si>
+  <si>
+    <t>0.6239,0.0476,0.1653,0.1093</t>
+  </si>
+  <si>
+    <t>0.8985,0.0295,0.0380,0.0183</t>
+  </si>
+  <si>
+    <t>0.9099,0.0380,0.0207,0.0056</t>
+  </si>
+  <si>
+    <t>0.2652,0.2549,0.2722,0.0005</t>
+  </si>
+  <si>
+    <t>0.8973,0.1259,0.0072,0.0013</t>
+  </si>
+  <si>
+    <t>0.9121,0.0909,0.0079,0.0010</t>
+  </si>
+  <si>
+    <t>0.9550,0.0343,0.0021,0.0014</t>
+  </si>
+  <si>
+    <t>0.9112,0.0924,0.0058,0.0009</t>
+  </si>
+  <si>
+    <t>0.9639,0.0183,0.0026,0.0022</t>
+  </si>
+  <si>
+    <t>0.9739,0.0157,0.0045,0.0004</t>
+  </si>
+  <si>
+    <t>0.9118,0.0836,0.0033,0.0018</t>
+  </si>
+  <si>
+    <t>0.3545,0.1264,0.6945,0.0275</t>
+  </si>
+  <si>
+    <t>0.9870,0.0034,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.8728,0.1155,0.0079,0.0024</t>
+  </si>
+  <si>
+    <t>0.6013,0.4479,0.0208,0.0013</t>
+  </si>
+  <si>
+    <t>0.9885,0.0078,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.8994,0.1474,0.0064,0.0006</t>
+  </si>
+  <si>
+    <t>0.7797,0.2538,0.0218,0.0019</t>
+  </si>
+  <si>
+    <t>0.9863,0.0068,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9737,0.0231,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9013,0.0899,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9569,0.0446,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9906,0.0046,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.8265,0.2086,0.0098,0.0013</t>
+  </si>
+  <si>
+    <t>0.9478,0.0617,0.0028,0.0008</t>
+  </si>
+  <si>
+    <t>0.8698,0.2157,0.0034,0.0004</t>
+  </si>
+  <si>
+    <t>0.9296,0.0592,0.0042,0.0014</t>
+  </si>
+  <si>
+    <t>0.9655,0.0261,0.0024,0.0014</t>
+  </si>
+  <si>
+    <t>0.9153,0.0907,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.8244,0.1875,0.0121,0.0028</t>
+  </si>
+  <si>
+    <t>0.7997,0.2918,0.0057,0.0007</t>
+  </si>
+  <si>
+    <t>0.9267,0.0726,0.0036,0.0007</t>
+  </si>
+  <si>
+    <t>0.9218,0.0609,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.9649,0.0282,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.7352,0.3215,0.0197,0.0028</t>
+  </si>
+  <si>
+    <t>0.7454,0.3660,0.0059,0.0008</t>
+  </si>
+  <si>
+    <t>0.0431,0.0342,0.9609,0.0004</t>
+  </si>
+  <si>
+    <t>0.9831,0.0156,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.8119,0.0040,0.3394,0.0004</t>
+  </si>
+  <si>
+    <t>0.9825,0.0006,0.0366,0.0001</t>
+  </si>
+  <si>
+    <t>0.8640,0.0871,0.0468,0.0016</t>
+  </si>
+  <si>
+    <t>0.4120,0.0097,0.7297,0.0003</t>
+  </si>
+  <si>
+    <t>0.7165,0.0041,0.4335,0.0008</t>
+  </si>
+  <si>
+    <t>0.9290,0.0021,0.1404,0.0005</t>
+  </si>
+  <si>
+    <t>0.9318,0.0109,0.0756,0.0005</t>
+  </si>
+  <si>
+    <t>0.9205,0.0376,0.0295,0.0009</t>
+  </si>
+  <si>
+    <t>0.9305,0.0081,0.0930,0.0020</t>
+  </si>
+  <si>
+    <t>0.9753,0.0070,0.0120,0.0008</t>
+  </si>
+  <si>
+    <t>0.7583,0.2073,0.0283,0.0003</t>
+  </si>
+  <si>
+    <t>0.9732,0.0145,0.0089,0.0002</t>
+  </si>
+  <si>
+    <t>0.6983,0.3473,0.0157,0.0002</t>
+  </si>
+  <si>
+    <t>0.9339,0.0341,0.0180,0.0010</t>
+  </si>
+  <si>
+    <t>0.9465,0.0228,0.0205,0.0008</t>
+  </si>
+  <si>
+    <t>0.9373,0.0767,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9458,0.0662,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9420,0.0969,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9578,0.0543,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9691,0.0229,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9600,0.0257,0.0074,0.0004</t>
+  </si>
+  <si>
+    <t>0.9702,0.0174,0.0058,0.0006</t>
+  </si>
+  <si>
+    <t>0.9870,0.0012,0.0103,0.0007</t>
+  </si>
+  <si>
+    <t>0.9782,0.0051,0.0147,0.0002</t>
+  </si>
+  <si>
+    <t>0.8813,0.0279,0.1188,0.0051</t>
+  </si>
+  <si>
+    <t>0.9161,0.0069,0.1234,0.0009</t>
+  </si>
+  <si>
+    <t>0.9541,0.0038,0.0734,0.0005</t>
+  </si>
+  <si>
+    <t>0.9905,0.0007,0.0094,0.0002</t>
+  </si>
+  <si>
+    <t>0.9792,0.0036,0.0167,0.0001</t>
+  </si>
+  <si>
+    <t>0.9733,0.0017,0.0395,0.0001</t>
+  </si>
+  <si>
+    <t>0.9715,0.0247,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9078,0.1077,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.8367,0.1788,0.0060,0.0023</t>
+  </si>
+  <si>
+    <t>0.7586,0.2988,0.0064,0.0011</t>
+  </si>
+  <si>
+    <t>0.8780,0.0994,0.0045,0.0034</t>
+  </si>
+  <si>
+    <t>0.9374,0.0658,0.0031,0.0010</t>
+  </si>
+  <si>
+    <t>0.9486,0.0432,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9555,0.0385,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9281,0.0280,0.0696,0.0034</t>
+  </si>
+  <si>
+    <t>0.9021,0.0810,0.0160,0.0009</t>
+  </si>
+  <si>
+    <t>0.9564,0.0396,0.0056,0.0010</t>
+  </si>
+  <si>
+    <t>0.4935,0.0114,0.7153,0.0006</t>
+  </si>
+  <si>
+    <t>0.0869,0.2948,0.6862,0.0010</t>
+  </si>
+  <si>
+    <t>0.6624,0.0329,0.4164,0.0020</t>
+  </si>
+  <si>
+    <t>0.3834,0.0086,0.8163,0.0001</t>
+  </si>
+  <si>
+    <t>0.9609,0.0052,0.0489,0.0008</t>
+  </si>
+  <si>
+    <t>0.0365,0.0127,0.9707,0.0006</t>
+  </si>
+  <si>
+    <t>0.9587,0.0026,0.0850,0.0002</t>
+  </si>
+  <si>
+    <t>0.9842,0.0028,0.0091,0.0003</t>
+  </si>
+  <si>
+    <t>0.9339,0.0208,0.0355,0.0015</t>
+  </si>
+  <si>
+    <t>0.9863,0.0023,0.0121,0.0003</t>
+  </si>
+  <si>
+    <t>0.9654,0.0216,0.0076,0.0005</t>
+  </si>
+  <si>
+    <t>0.7357,0.2774,0.0064,0.0025</t>
+  </si>
+  <si>
+    <t>0.8757,0.1835,0.0023,0.0008</t>
+  </si>
+  <si>
+    <t>0.9011,0.0977,0.0033,0.0012</t>
+  </si>
+  <si>
+    <t>0.9679,0.0375,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9095,0.0782,0.0032,0.0018</t>
+  </si>
+  <si>
+    <t>0.9512,0.0557,0.0027,0.0005</t>
+  </si>
+  <si>
+    <t>0.8149,0.2401,0.0052,0.0016</t>
+  </si>
+  <si>
+    <t>0.7507,0.3837,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.9845,0.0020,0.0198,0.0001</t>
+  </si>
+  <si>
+    <t>0.0946,0.0079,0.9601,0.0004</t>
+  </si>
+  <si>
+    <t>0.4306,0.0578,0.4689,0.0014</t>
+  </si>
+  <si>
+    <t>0.9887,0.0013,0.0130,0.0001</t>
+  </si>
+  <si>
+    <t>0.5652,0.0032,0.6598,0.0009</t>
+  </si>
+  <si>
+    <t>0.9233,0.0198,0.0598,0.0011</t>
+  </si>
+  <si>
+    <t>0.9920,0.0012,0.0062,0.0001</t>
+  </si>
+  <si>
+    <t>0.9872,0.0016,0.0103,0.0001</t>
+  </si>
+  <si>
+    <t>0.9600,0.0174,0.0029,0.0032</t>
+  </si>
+  <si>
+    <t>0.8925,0.0162,0.0890,0.0115</t>
+  </si>
+  <si>
+    <t>0.9775,0.0069,0.0027,0.0023</t>
+  </si>
+  <si>
+    <t>0.9839,0.0021,0.0048,0.0016</t>
+  </si>
+  <si>
+    <t>0.9715,0.0021,0.0035,0.0133</t>
+  </si>
+  <si>
+    <t>0.9341,0.0444,0.0098,0.0015</t>
   </si>
 </sst>
 </file>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9672,0.0207,0.0067,0.0008</t>
-  </si>
-  <si>
-    <t>0.8876,0.0480,0.0340,0.0118</t>
-  </si>
-  <si>
-    <t>0.9710,0.0207,0.0033,0.0007</t>
-  </si>
-  <si>
-    <t>0.9702,0.0125,0.0018,0.0016</t>
-  </si>
-  <si>
-    <t>0.9853,0.0087,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9556,0.0364,0.0019,0.0011</t>
-  </si>
-  <si>
-    <t>0.8497,0.1237,0.0051,0.0028</t>
-  </si>
-  <si>
-    <t>0.8908,0.1069,0.0072,0.0028</t>
-  </si>
-  <si>
-    <t>0.9795,0.0183,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9643,0.0169,0.0012,0.0022</t>
-  </si>
-  <si>
-    <t>0.9521,0.0349,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.9184,0.1002,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9688,0.0129,0.0144,0.0004</t>
-  </si>
-  <si>
-    <t>0.9170,0.0399,0.0259,0.0006</t>
-  </si>
-  <si>
-    <t>0.9648,0.0159,0.0098,0.0002</t>
-  </si>
-  <si>
-    <t>0.6659,0.0393,0.3916,0.0034</t>
-  </si>
-  <si>
-    <t>0.9283,0.0886,0.0047,0.0006</t>
-  </si>
-  <si>
-    <t>0.6430,0.5136,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.6471,0.4641,0.0079,0.0004</t>
-  </si>
-  <si>
-    <t>0.8335,0.2431,0.0055,0.0004</t>
-  </si>
-  <si>
-    <t>0.2095,0.8719,0.0054,0.0008</t>
-  </si>
-  <si>
-    <t>0.4744,0.6785,0.0065,0.0007</t>
-  </si>
-  <si>
-    <t>0.9020,0.0194,0.1004,0.0011</t>
-  </si>
-  <si>
-    <t>0.9806,0.0009,0.0348,0.0002</t>
-  </si>
-  <si>
-    <t>0.9246,0.0071,0.1032,0.0005</t>
-  </si>
-  <si>
-    <t>0.9808,0.0028,0.0227,0.0001</t>
-  </si>
-  <si>
-    <t>0.9736,0.0038,0.0273,0.0007</t>
-  </si>
-  <si>
-    <t>0.9836,0.0015,0.0194,0.0003</t>
-  </si>
-  <si>
-    <t>0.5919,0.0042,0.6033,0.0016</t>
-  </si>
-  <si>
-    <t>0.7581,0.4499,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.9234,0.0573,0.0196,0.0008</t>
-  </si>
-  <si>
-    <t>0.0723,0.0413,0.9334,0.0025</t>
-  </si>
-  <si>
-    <t>0.5474,0.4169,0.0268,0.0002</t>
-  </si>
-  <si>
-    <t>0.9858,0.0078,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9614,0.0412,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.9644,0.0476,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9780,0.0245,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.4685,0.0878,0.3558,0.0026</t>
-  </si>
-  <si>
-    <t>0.9590,0.0021,0.0828,0.0009</t>
-  </si>
-  <si>
-    <t>0.9837,0.0017,0.0223,0.0001</t>
-  </si>
-  <si>
-    <t>0.9902,0.0015,0.0099,0.0002</t>
-  </si>
-  <si>
-    <t>0.8987,0.0016,0.2515,0.0002</t>
-  </si>
-  <si>
-    <t>0.2020,0.0140,0.7223,0.0027</t>
-  </si>
-  <si>
-    <t>0.8363,0.0009,0.3741,0.0002</t>
-  </si>
-  <si>
-    <t>0.9012,0.0943,0.0068,0.0009</t>
-  </si>
-  <si>
-    <t>0.6763,0.4804,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.9527,0.0366,0.0062,0.0001</t>
-  </si>
-  <si>
-    <t>0.9546,0.0368,0.0053,0.0000</t>
-  </si>
-  <si>
-    <t>0.1825,0.0517,0.8166,0.0064</t>
-  </si>
-  <si>
-    <t>0.5288,0.0152,0.5441,0.0002</t>
-  </si>
-  <si>
-    <t>0.9048,0.0204,0.0995,0.0016</t>
-  </si>
-  <si>
-    <t>0.9792,0.0035,0.0179,0.0003</t>
-  </si>
-  <si>
-    <t>0.0557,0.0151,0.9044,0.0015</t>
-  </si>
-  <si>
-    <t>0.6486,0.0212,0.3344,0.0007</t>
-  </si>
-  <si>
-    <t>0.9220,0.0858,0.0034,0.0011</t>
-  </si>
-  <si>
-    <t>0.9203,0.0607,0.0071,0.0022</t>
-  </si>
-  <si>
-    <t>0.9705,0.0126,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.0128,0.8709,0.8452,0.0008</t>
-  </si>
-  <si>
-    <t>0.8646,0.1603,0.0078,0.0012</t>
-  </si>
-  <si>
-    <t>0.9777,0.0127,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.8694,0.1716,0.0074,0.0013</t>
-  </si>
-  <si>
-    <t>0.0527,0.0245,0.9615,0.0008</t>
-  </si>
-  <si>
-    <t>0.1443,0.0012,0.9525,0.0002</t>
-  </si>
-  <si>
-    <t>0.9737,0.0016,0.0572,0.0002</t>
-  </si>
-  <si>
-    <t>0.3211,0.5560,0.0653,0.0001</t>
-  </si>
-  <si>
-    <t>0.0981,0.0099,0.9521,0.0004</t>
-  </si>
-  <si>
-    <t>0.7369,0.3439,0.0097,0.0002</t>
-  </si>
-  <si>
-    <t>0.5428,0.6959,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9240,0.0961,0.0058,0.0005</t>
-  </si>
-  <si>
-    <t>0.9647,0.0301,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.1715,0.2127,0.8273,0.0043</t>
-  </si>
-  <si>
-    <t>0.6458,0.0516,0.4462,0.0010</t>
-  </si>
-  <si>
-    <t>0.9069,0.0318,0.0618,0.0003</t>
-  </si>
-  <si>
-    <t>0.2877,0.5705,0.0596,0.0001</t>
-  </si>
-  <si>
-    <t>0.5226,0.2319,0.1230,0.0005</t>
-  </si>
-  <si>
-    <t>0.9524,0.0149,0.0164,0.0048</t>
-  </si>
-  <si>
-    <t>0.9293,0.0173,0.0097,0.0122</t>
-  </si>
-  <si>
-    <t>0.9894,0.0033,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9736,0.0098,0.0025,0.0025</t>
-  </si>
-  <si>
-    <t>0.9583,0.0160,0.0084,0.0031</t>
-  </si>
-  <si>
-    <t>0.9626,0.0097,0.0117,0.0045</t>
-  </si>
-  <si>
-    <t>0.9288,0.0256,0.0458,0.0006</t>
-  </si>
-  <si>
-    <t>0.9521,0.0134,0.0430,0.0002</t>
-  </si>
-  <si>
-    <t>0.6172,0.0142,0.3994,0.0004</t>
-  </si>
-  <si>
-    <t>0.3325,0.0070,0.8211,0.0003</t>
-  </si>
-  <si>
-    <t>0.7183,0.0801,0.0859,0.0004</t>
-  </si>
-  <si>
-    <t>0.9881,0.0020,0.0081,0.0001</t>
-  </si>
-  <si>
-    <t>0.9726,0.0213,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.9409,0.0721,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.9234,0.1020,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9443,0.0511,0.0018,0.0011</t>
-  </si>
-  <si>
-    <t>0.9116,0.0879,0.0042,0.0015</t>
-  </si>
-  <si>
-    <t>0.9449,0.0381,0.0031,0.0016</t>
-  </si>
-  <si>
-    <t>0.9312,0.0691,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.8507,0.2012,0.0048,0.0010</t>
-  </si>
-  <si>
-    <t>0.9510,0.0300,0.0014,0.0017</t>
-  </si>
-  <si>
-    <t>0.9595,0.0287,0.0023,0.0010</t>
-  </si>
-  <si>
-    <t>0.9568,0.0322,0.0041,0.0013</t>
-  </si>
-  <si>
-    <t>0.9862,0.0074,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.8678,0.1810,0.0044,0.0010</t>
-  </si>
-  <si>
-    <t>0.9711,0.0218,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9426,0.0649,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9595,0.0308,0.0025,0.0017</t>
-  </si>
-  <si>
-    <t>0.0724,0.0090,0.9632,0.0005</t>
-  </si>
-  <si>
-    <t>0.9772,0.0029,0.0354,0.0004</t>
-  </si>
-  <si>
-    <t>0.9604,0.0168,0.0101,0.0017</t>
-  </si>
-  <si>
-    <t>0.5757,0.0648,0.2646,0.0006</t>
-  </si>
-  <si>
-    <t>0.6468,0.5508,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.5855,0.5114,0.0136,0.0017</t>
-  </si>
-  <si>
-    <t>0.7362,0.3547,0.0120,0.0006</t>
-  </si>
-  <si>
-    <t>0.9011,0.1326,0.0036,0.0008</t>
-  </si>
-  <si>
-    <t>0.0813,0.9387,0.0097,0.0003</t>
-  </si>
-  <si>
-    <t>0.1316,0.9194,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.8750,0.1706,0.0034,0.0007</t>
-  </si>
-  <si>
-    <t>0.9191,0.0717,0.0117,0.0004</t>
-  </si>
-  <si>
-    <t>0.9544,0.0077,0.0635,0.0004</t>
-  </si>
-  <si>
-    <t>0.9738,0.0123,0.0083,0.0004</t>
-  </si>
-  <si>
-    <t>0.9638,0.0235,0.0088,0.0002</t>
-  </si>
-  <si>
-    <t>0.8372,0.1319,0.0248,0.0039</t>
-  </si>
-  <si>
-    <t>0.8932,0.1212,0.0060,0.0000</t>
-  </si>
-  <si>
-    <t>0.9492,0.0518,0.0037,0.0000</t>
-  </si>
-  <si>
-    <t>0.9472,0.0561,0.0062,0.0003</t>
-  </si>
-  <si>
-    <t>0.2825,0.1529,0.3061,0.0004</t>
-  </si>
-  <si>
-    <t>0.9627,0.0434,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.8496,0.1421,0.0210,0.0011</t>
-  </si>
-  <si>
-    <t>0.8445,0.1888,0.0088,0.0015</t>
-  </si>
-  <si>
-    <t>0.9194,0.0787,0.0034,0.0009</t>
-  </si>
-  <si>
-    <t>0.9431,0.0804,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9502,0.0564,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.8778,0.0983,0.0129,0.0028</t>
-  </si>
-  <si>
-    <t>0.8191,0.2665,0.0057,0.0009</t>
-  </si>
-  <si>
-    <t>0.9795,0.0128,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.8384,0.1789,0.0119,0.0023</t>
-  </si>
-  <si>
-    <t>0.8932,0.1258,0.0034,0.0006</t>
-  </si>
-  <si>
-    <t>0.8516,0.0133,0.2139,0.0008</t>
-  </si>
-  <si>
-    <t>0.8777,0.0099,0.1514,0.0004</t>
-  </si>
-  <si>
-    <t>0.9170,0.0063,0.1475,0.0003</t>
-  </si>
-  <si>
-    <t>0.9914,0.0005,0.0120,0.0001</t>
-  </si>
-  <si>
-    <t>0.9918,0.0024,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.9907,0.0037,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9630,0.0180,0.0119,0.0004</t>
-  </si>
-  <si>
-    <t>0.9737,0.0146,0.0046,0.0005</t>
-  </si>
-  <si>
-    <t>0.9753,0.0072,0.0041,0.0022</t>
-  </si>
-  <si>
-    <t>0.6239,0.0476,0.1653,0.1093</t>
-  </si>
-  <si>
-    <t>0.8985,0.0295,0.0380,0.0183</t>
-  </si>
-  <si>
-    <t>0.9099,0.0380,0.0207,0.0056</t>
-  </si>
-  <si>
-    <t>0.2652,0.2549,0.2722,0.0005</t>
-  </si>
-  <si>
-    <t>0.8973,0.1259,0.0072,0.0013</t>
-  </si>
-  <si>
-    <t>0.9121,0.0909,0.0079,0.0010</t>
-  </si>
-  <si>
-    <t>0.9550,0.0343,0.0021,0.0014</t>
-  </si>
-  <si>
-    <t>0.9112,0.0924,0.0058,0.0009</t>
-  </si>
-  <si>
-    <t>0.9639,0.0183,0.0026,0.0022</t>
-  </si>
-  <si>
-    <t>0.9739,0.0157,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.9118,0.0836,0.0033,0.0018</t>
-  </si>
-  <si>
-    <t>0.3545,0.1264,0.6945,0.0275</t>
-  </si>
-  <si>
-    <t>0.9870,0.0034,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.8728,0.1155,0.0079,0.0024</t>
-  </si>
-  <si>
-    <t>0.6013,0.4479,0.0208,0.0013</t>
-  </si>
-  <si>
-    <t>0.9885,0.0078,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.8994,0.1474,0.0064,0.0006</t>
-  </si>
-  <si>
-    <t>0.7797,0.2538,0.0218,0.0019</t>
-  </si>
-  <si>
-    <t>0.9863,0.0068,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9737,0.0231,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9013,0.0899,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9569,0.0446,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9906,0.0046,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.8265,0.2086,0.0098,0.0013</t>
-  </si>
-  <si>
-    <t>0.9478,0.0617,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.8698,0.2157,0.0034,0.0004</t>
-  </si>
-  <si>
-    <t>0.9296,0.0592,0.0042,0.0014</t>
-  </si>
-  <si>
-    <t>0.9655,0.0261,0.0024,0.0014</t>
-  </si>
-  <si>
-    <t>0.9153,0.0907,0.0047,0.0006</t>
-  </si>
-  <si>
-    <t>0.8244,0.1875,0.0121,0.0028</t>
-  </si>
-  <si>
-    <t>0.7997,0.2918,0.0057,0.0007</t>
-  </si>
-  <si>
-    <t>0.9267,0.0726,0.0036,0.0007</t>
-  </si>
-  <si>
-    <t>0.9218,0.0609,0.0024,0.0018</t>
-  </si>
-  <si>
-    <t>0.9649,0.0282,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.7352,0.3215,0.0197,0.0028</t>
-  </si>
-  <si>
-    <t>0.7454,0.3660,0.0059,0.0008</t>
-  </si>
-  <si>
-    <t>0.0431,0.0342,0.9609,0.0004</t>
-  </si>
-  <si>
-    <t>0.9831,0.0156,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.8119,0.0040,0.3394,0.0004</t>
-  </si>
-  <si>
-    <t>0.9825,0.0006,0.0366,0.0001</t>
-  </si>
-  <si>
-    <t>0.8640,0.0871,0.0468,0.0016</t>
-  </si>
-  <si>
-    <t>0.4120,0.0097,0.7297,0.0003</t>
-  </si>
-  <si>
-    <t>0.7165,0.0041,0.4335,0.0008</t>
-  </si>
-  <si>
-    <t>0.9290,0.0021,0.1404,0.0005</t>
-  </si>
-  <si>
-    <t>0.9318,0.0109,0.0756,0.0005</t>
-  </si>
-  <si>
-    <t>0.9205,0.0376,0.0295,0.0009</t>
-  </si>
-  <si>
-    <t>0.9305,0.0081,0.0930,0.0020</t>
-  </si>
-  <si>
-    <t>0.9753,0.0070,0.0120,0.0008</t>
-  </si>
-  <si>
-    <t>0.7583,0.2073,0.0283,0.0003</t>
-  </si>
-  <si>
-    <t>0.9732,0.0145,0.0089,0.0002</t>
-  </si>
-  <si>
-    <t>0.6983,0.3473,0.0157,0.0002</t>
-  </si>
-  <si>
-    <t>0.9339,0.0341,0.0180,0.0010</t>
-  </si>
-  <si>
-    <t>0.9465,0.0228,0.0205,0.0008</t>
-  </si>
-  <si>
-    <t>0.9373,0.0767,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9458,0.0662,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9420,0.0969,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9578,0.0543,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9691,0.0229,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9600,0.0257,0.0074,0.0004</t>
-  </si>
-  <si>
-    <t>0.9702,0.0174,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.9870,0.0012,0.0103,0.0007</t>
-  </si>
-  <si>
-    <t>0.9782,0.0051,0.0147,0.0002</t>
-  </si>
-  <si>
-    <t>0.8813,0.0279,0.1188,0.0051</t>
-  </si>
-  <si>
-    <t>0.9161,0.0069,0.1234,0.0009</t>
-  </si>
-  <si>
-    <t>0.9541,0.0038,0.0734,0.0005</t>
-  </si>
-  <si>
-    <t>0.9905,0.0007,0.0094,0.0002</t>
-  </si>
-  <si>
-    <t>0.9792,0.0036,0.0167,0.0001</t>
-  </si>
-  <si>
-    <t>0.9733,0.0017,0.0395,0.0001</t>
-  </si>
-  <si>
-    <t>0.9715,0.0247,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9078,0.1077,0.0022,0.0010</t>
-  </si>
-  <si>
-    <t>0.8367,0.1788,0.0060,0.0023</t>
-  </si>
-  <si>
-    <t>0.7586,0.2988,0.0064,0.0011</t>
-  </si>
-  <si>
-    <t>0.8780,0.0994,0.0045,0.0034</t>
-  </si>
-  <si>
-    <t>0.9374,0.0658,0.0031,0.0010</t>
-  </si>
-  <si>
-    <t>0.9486,0.0432,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9555,0.0385,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9281,0.0280,0.0696,0.0034</t>
-  </si>
-  <si>
-    <t>0.9021,0.0810,0.0160,0.0009</t>
-  </si>
-  <si>
-    <t>0.9564,0.0396,0.0056,0.0010</t>
-  </si>
-  <si>
-    <t>0.4935,0.0114,0.7153,0.0006</t>
-  </si>
-  <si>
-    <t>0.0869,0.2948,0.6862,0.0010</t>
-  </si>
-  <si>
-    <t>0.6624,0.0329,0.4164,0.0020</t>
-  </si>
-  <si>
-    <t>0.3834,0.0086,0.8163,0.0001</t>
-  </si>
-  <si>
-    <t>0.9609,0.0052,0.0489,0.0008</t>
-  </si>
-  <si>
-    <t>0.0365,0.0127,0.9707,0.0006</t>
-  </si>
-  <si>
-    <t>0.9587,0.0026,0.0850,0.0002</t>
-  </si>
-  <si>
-    <t>0.9842,0.0028,0.0091,0.0003</t>
-  </si>
-  <si>
-    <t>0.9339,0.0208,0.0355,0.0015</t>
-  </si>
-  <si>
-    <t>0.9863,0.0023,0.0121,0.0003</t>
-  </si>
-  <si>
-    <t>0.9654,0.0216,0.0076,0.0005</t>
-  </si>
-  <si>
-    <t>0.7357,0.2774,0.0064,0.0025</t>
-  </si>
-  <si>
-    <t>0.8757,0.1835,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.9011,0.0977,0.0033,0.0012</t>
-  </si>
-  <si>
-    <t>0.9679,0.0375,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9095,0.0782,0.0032,0.0018</t>
-  </si>
-  <si>
-    <t>0.9512,0.0557,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.8149,0.2401,0.0052,0.0016</t>
-  </si>
-  <si>
-    <t>0.7507,0.3837,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.9845,0.0020,0.0198,0.0001</t>
-  </si>
-  <si>
-    <t>0.0946,0.0079,0.9601,0.0004</t>
-  </si>
-  <si>
-    <t>0.4306,0.0578,0.4689,0.0014</t>
-  </si>
-  <si>
-    <t>0.9887,0.0013,0.0130,0.0001</t>
-  </si>
-  <si>
-    <t>0.5652,0.0032,0.6598,0.0009</t>
-  </si>
-  <si>
-    <t>0.9233,0.0198,0.0598,0.0011</t>
-  </si>
-  <si>
-    <t>0.9920,0.0012,0.0062,0.0001</t>
-  </si>
-  <si>
-    <t>0.9872,0.0016,0.0103,0.0001</t>
-  </si>
-  <si>
-    <t>0.9600,0.0174,0.0029,0.0032</t>
-  </si>
-  <si>
-    <t>0.8925,0.0162,0.0890,0.0115</t>
-  </si>
-  <si>
-    <t>0.9775,0.0069,0.0027,0.0023</t>
-  </si>
-  <si>
-    <t>0.9839,0.0021,0.0048,0.0016</t>
-  </si>
-  <si>
-    <t>0.9715,0.0021,0.0035,0.0133</t>
-  </si>
-  <si>
-    <t>0.9341,0.0444,0.0098,0.0015</t>
+    <t>0.9889,0.0014,0.0030,0.0028</t>
+  </si>
+  <si>
+    <t>0.0121,0.0048,0.0001,0.9948</t>
+  </si>
+  <si>
+    <t>0.9145,0.0028,0.0021,0.0971</t>
+  </si>
+  <si>
+    <t>0.1362,0.0072,0.0010,0.9479</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0007,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0043,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.8423,0.0364,0.1088,0.0039</t>
+  </si>
+  <si>
+    <t>0.2742,0.0261,0.7447,0.0167</t>
+  </si>
+  <si>
+    <t>0.2678,0.0033,0.9087,0.0002</t>
+  </si>
+  <si>
+    <t>0.0494,0.0041,0.9368,0.0108</t>
+  </si>
+  <si>
+    <t>0.9786,0.0038,0.0208,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.9974,0.0027,0.0008</t>
+  </si>
+  <si>
+    <t>0.0150,0.9788,0.0022,0.0092</t>
+  </si>
+  <si>
+    <t>0.0733,0.9305,0.0241,0.0030</t>
+  </si>
+  <si>
+    <t>0.0030,0.9932,0.0030,0.0026</t>
+  </si>
+  <si>
+    <t>0.0019,0.9932,0.0113,0.0030</t>
+  </si>
+  <si>
+    <t>0.9278,0.0006,0.1625,0.0007</t>
+  </si>
+  <si>
+    <t>0.4305,0.0016,0.6785,0.0035</t>
+  </si>
+  <si>
+    <t>0.0118,0.0044,0.9889,0.0008</t>
+  </si>
+  <si>
+    <t>0.0103,0.0010,0.9896,0.0008</t>
+  </si>
+  <si>
+    <t>0.0130,0.0020,0.9893,0.0010</t>
+  </si>
+  <si>
+    <t>0.0993,0.0048,0.9327,0.0023</t>
+  </si>
+  <si>
+    <t>0.0020,0.0006,0.9973,0.0003</t>
+  </si>
+  <si>
+    <t>0.1585,0.8956,0.0047,0.0133</t>
+  </si>
+  <si>
+    <t>0.4184,0.4393,0.2478,0.0191</t>
+  </si>
+  <si>
+    <t>0.0007,0.0018,0.9973,0.0029</t>
+  </si>
+  <si>
+    <t>0.0114,0.4631,0.6966,0.0003</t>
+  </si>
+  <si>
+    <t>0.9377,0.0289,0.0197,0.0127</t>
+  </si>
+  <si>
+    <t>0.9237,0.0296,0.0503,0.0027</t>
+  </si>
+  <si>
+    <t>0.9702,0.0483,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0179,0.9819,0.0106,0.0002</t>
+  </si>
+  <si>
+    <t>0.0155,0.0398,0.9243,0.0411</t>
+  </si>
+  <si>
+    <t>0.0218,0.0033,0.9791,0.0026</t>
+  </si>
+  <si>
+    <t>0.0201,0.0126,0.9781,0.0011</t>
+  </si>
+  <si>
+    <t>0.0632,0.0012,0.8546,0.0413</t>
+  </si>
+  <si>
+    <t>0.0077,0.1772,0.9848,0.0011</t>
+  </si>
+  <si>
+    <t>0.0293,0.6740,0.2271,0.0004</t>
+  </si>
+  <si>
+    <t>0.0052,0.0009,0.9947,0.0007</t>
+  </si>
+  <si>
+    <t>0.4949,0.2982,0.0114,0.2062</t>
+  </si>
+  <si>
+    <t>0.0024,0.9882,0.0043,0.0129</t>
+  </si>
+  <si>
+    <t>0.0059,0.9824,0.0197,0.0023</t>
+  </si>
+  <si>
+    <t>0.0085,0.9782,0.0295,0.0052</t>
+  </si>
+  <si>
+    <t>0.0014,0.0021,0.9895,0.0089</t>
+  </si>
+  <si>
+    <t>0.0015,0.0808,0.9885,0.0040</t>
+  </si>
+  <si>
+    <t>0.4596,0.0032,0.7039,0.0022</t>
+  </si>
+  <si>
+    <t>0.0100,0.0020,0.9886,0.0015</t>
+  </si>
+  <si>
+    <t>0.0139,0.0013,0.9921,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0070,0.9960,0.0004</t>
+  </si>
+  <si>
+    <t>0.9575,0.0674,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9884,0.0040,0.0052,0.0014</t>
+  </si>
+  <si>
+    <t>0.9922,0.0054,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.0188,0.0095,0.9865,0.0011</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0020,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9788,0.0239,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.0017,0.6070,0.9867,0.0014</t>
+  </si>
+  <si>
+    <t>0.0052,0.0003,0.9937,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.0025,0.9980,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.9664,0.9343,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.0023,0.9939,0.0017</t>
+  </si>
+  <si>
+    <t>0.0217,0.9708,0.0411,0.0007</t>
+  </si>
+  <si>
+    <t>0.0116,0.9912,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9939,0.0009,0.0052,0.0004</t>
+  </si>
+  <si>
+    <t>0.1194,0.2267,0.8527,0.0042</t>
+  </si>
+  <si>
+    <t>0.0033,0.0260,0.9942,0.0031</t>
+  </si>
+  <si>
+    <t>0.0121,0.3303,0.9301,0.0017</t>
+  </si>
+  <si>
+    <t>0.0026,0.6629,0.9811,0.0008</t>
+  </si>
+  <si>
+    <t>0.0041,0.9809,0.3909,0.0019</t>
+  </si>
+  <si>
+    <t>0.0013,0.9889,0.5334,0.0005</t>
+  </si>
+  <si>
+    <t>0.0059,0.0002,0.0070,0.9922</t>
+  </si>
+  <si>
+    <t>0.0015,0.0042,0.0005,0.9984</t>
+  </si>
+  <si>
+    <t>0.0092,0.0037,0.0002,0.9959</t>
+  </si>
+  <si>
+    <t>0.0252,0.0023,0.0028,0.9878</t>
+  </si>
+  <si>
+    <t>0.0029,0.0031,0.0025,0.9966</t>
+  </si>
+  <si>
+    <t>0.0213,0.0080,0.0009,0.9904</t>
+  </si>
+  <si>
+    <t>0.0010,0.9788,0.9297,0.0006</t>
+  </si>
+  <si>
+    <t>0.0028,0.1709,0.9956,0.0002</t>
+  </si>
+  <si>
+    <t>0.0121,0.5700,0.8432,0.0018</t>
+  </si>
+  <si>
+    <t>0.0036,0.5236,0.9778,0.0015</t>
+  </si>
+  <si>
+    <t>0.0013,0.7694,0.9820,0.0006</t>
+  </si>
+  <si>
+    <t>0.0030,0.9705,0.1418,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0038,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9834,0.0148,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9957,0.0015,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9964,0.0008,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9918,0.0046,0.0014,0.0014</t>
+  </si>
+  <si>
+    <t>0.9983,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0012,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0030,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0055,0.0031,0.9937,0.0012</t>
+  </si>
+  <si>
+    <t>0.0135,0.0027,0.9844,0.0022</t>
+  </si>
+  <si>
+    <t>0.9597,0.0025,0.0463,0.0028</t>
+  </si>
+  <si>
+    <t>0.0046,0.0005,0.9961,0.0004</t>
+  </si>
+  <si>
+    <t>0.0044,0.9936,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.9958,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.0074,0.9905,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.1159,0.8917,0.0133,0.0141</t>
+  </si>
+  <si>
+    <t>0.0105,0.9890,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.0035,0.9925,0.0071,0.0009</t>
+  </si>
+  <si>
+    <t>0.8555,0.2443,0.0035,0.0019</t>
+  </si>
+  <si>
+    <t>0.4968,0.3375,0.0560,0.0781</t>
+  </si>
+  <si>
+    <t>0.2805,0.0043,0.7920,0.0056</t>
+  </si>
+  <si>
+    <t>0.5624,0.0256,0.4859,0.0194</t>
+  </si>
+  <si>
+    <t>0.6469,0.0166,0.4340,0.0106</t>
+  </si>
+  <si>
+    <t>0.0485,0.0477,0.3092,0.8106</t>
+  </si>
+  <si>
+    <t>0.0011,0.9957,0.0048,0.0027</t>
+  </si>
+  <si>
+    <t>0.0047,0.9899,0.0044,0.0016</t>
+  </si>
+  <si>
+    <t>0.0005,0.9973,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.0029,0.6370,0.9387,0.0024</t>
+  </si>
+  <si>
+    <t>0.0192,0.9747,0.0111,0.0007</t>
+  </si>
+  <si>
+    <t>0.9635,0.0263,0.0117,0.0016</t>
+  </si>
+  <si>
+    <t>0.6938,0.3592,0.0096,0.0062</t>
+  </si>
+  <si>
+    <t>0.9945,0.0032,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9865,0.0056,0.0047,0.0014</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9917,0.0014,0.0069,0.0008</t>
+  </si>
+  <si>
+    <t>0.9954,0.0006,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.0048,0.7260,0.9620,0.0041</t>
+  </si>
+  <si>
+    <t>0.0020,0.5384,0.9897,0.0004</t>
+  </si>
+  <si>
+    <t>0.0050,0.0217,0.9838,0.0022</t>
+  </si>
+  <si>
+    <t>0.0209,0.0370,0.9724,0.0042</t>
+  </si>
+  <si>
+    <t>0.9709,0.0026,0.0326,0.0013</t>
+  </si>
+  <si>
+    <t>0.9620,0.0034,0.0298,0.0042</t>
+  </si>
+  <si>
+    <t>0.1473,0.0067,0.8871,0.0056</t>
+  </si>
+  <si>
+    <t>0.8760,0.0194,0.1525,0.0096</t>
+  </si>
+  <si>
+    <t>0.0609,0.0004,0.0003,0.9883</t>
+  </si>
+  <si>
+    <t>0.0005,0.0018,0.0126,0.9969</t>
+  </si>
+  <si>
+    <t>0.0011,0.0094,0.0013,0.9981</t>
+  </si>
+  <si>
+    <t>0.0223,0.0005,0.0028,0.9895</t>
+  </si>
+  <si>
+    <t>0.0040,0.9488,0.5343,0.0039</t>
+  </si>
+  <si>
+    <t>0.9958,0.0009,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.8701,0.1855,0.0014,0.0019</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.2007,0.8708,0.0020,0.0040</t>
+  </si>
+  <si>
+    <t>0.9871,0.0004,0.0045,0.0035</t>
+  </si>
+  <si>
+    <t>0.4230,0.0093,0.0026,0.7392</t>
+  </si>
+  <si>
+    <t>0.9903,0.0009,0.0087,0.0004</t>
+  </si>
+  <si>
+    <t>0.0048,0.0039,0.9628,0.1182</t>
+  </si>
+  <si>
+    <t>0.9218,0.0004,0.0014,0.1514</t>
+  </si>
+  <si>
+    <t>0.9865,0.0004,0.0009,0.0119</t>
+  </si>
+  <si>
+    <t>0.6861,0.3081,0.0816,0.0123</t>
+  </si>
+  <si>
+    <t>0.9882,0.0028,0.0023,0.0014</t>
+  </si>
+  <si>
+    <t>0.9881,0.0031,0.0060,0.0011</t>
+  </si>
+  <si>
+    <t>0.1682,0.7760,0.0299,0.0523</t>
+  </si>
+  <si>
+    <t>0.8986,0.0249,0.0898,0.0023</t>
+  </si>
+  <si>
+    <t>0.9861,0.0064,0.0042,0.0008</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9904,0.0037,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.9912,0.0022,0.0022,0.0032</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9952,0.0016,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9941,0.0008,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9570,0.0454,0.0024,0.0026</t>
+  </si>
+  <si>
+    <t>0.5387,0.6332,0.0035,0.0009</t>
+  </si>
+  <si>
+    <t>0.9160,0.1171,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.8747,0.0952,0.0498,0.0017</t>
+  </si>
+  <si>
+    <t>0.9962,0.0029,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9347,0.0382,0.0255,0.0052</t>
+  </si>
+  <si>
+    <t>0.9942,0.0034,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9875,0.0075,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.0043,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.9794,0.0094,0.0104,0.0020</t>
+  </si>
+  <si>
+    <t>0.0027,0.0010,0.9944,0.0011</t>
+  </si>
+  <si>
+    <t>0.0022,0.0351,0.9927,0.0048</t>
+  </si>
+  <si>
+    <t>0.0143,0.0015,0.9842,0.0022</t>
+  </si>
+  <si>
+    <t>0.0018,0.0156,0.9958,0.0027</t>
+  </si>
+  <si>
+    <t>0.1041,0.0190,0.8986,0.0021</t>
+  </si>
+  <si>
+    <t>0.0035,0.0003,0.9966,0.0002</t>
+  </si>
+  <si>
+    <t>0.0165,0.0599,0.9753,0.0120</t>
+  </si>
+  <si>
+    <t>0.4473,0.0191,0.5906,0.0173</t>
+  </si>
+  <si>
+    <t>0.1391,0.0277,0.8884,0.0024</t>
+  </si>
+  <si>
+    <t>0.8952,0.0048,0.1946,0.0009</t>
+  </si>
+  <si>
+    <t>0.2472,0.0144,0.8062,0.0009</t>
+  </si>
+  <si>
+    <t>0.0705,0.0355,0.8874,0.0015</t>
+  </si>
+  <si>
+    <t>0.3347,0.0388,0.6726,0.0016</t>
+  </si>
+  <si>
+    <t>0.7523,0.0328,0.2157,0.0432</t>
+  </si>
+  <si>
+    <t>0.1428,0.0720,0.7732,0.0078</t>
+  </si>
+  <si>
+    <t>0.2504,0.9025,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0683,0.9543,0.0014,0.0031</t>
+  </si>
+  <si>
+    <t>0.7985,0.3566,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9568,0.0488,0.0043,0.0025</t>
+  </si>
+  <si>
+    <t>0.6607,0.6251,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9384,0.0223,0.0292,0.0009</t>
+  </si>
+  <si>
+    <t>0.9909,0.0009,0.0024,0.0015</t>
+  </si>
+  <si>
+    <t>0.9571,0.0038,0.0132,0.0118</t>
+  </si>
+  <si>
+    <t>0.7793,0.0128,0.3012,0.0044</t>
+  </si>
+  <si>
+    <t>0.6965,0.0021,0.2859,0.0098</t>
+  </si>
+  <si>
+    <t>0.0034,0.0017,0.9930,0.0028</t>
+  </si>
+  <si>
+    <t>0.0098,0.0059,0.9807,0.0042</t>
+  </si>
+  <si>
+    <t>0.0573,0.0950,0.9088,0.0078</t>
+  </si>
+  <si>
+    <t>0.0587,0.0074,0.9666,0.0007</t>
+  </si>
+  <si>
+    <t>0.0544,0.0853,0.8662,0.0061</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9944,0.0014,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9918,0.0022,0.0005,0.0028</t>
+  </si>
+  <si>
+    <t>0.9840,0.0171,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.9803,0.0208,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9966,0.0021,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9971,0.0007,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0005,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.0015,0.0091,0.9975,0.0007</t>
+  </si>
+  <si>
+    <t>0.1716,0.3528,0.4672,0.0015</t>
+  </si>
+  <si>
+    <t>0.9639,0.0083,0.0186,0.0064</t>
+  </si>
+  <si>
+    <t>0.0046,0.0005,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0052,0.9976,0.0026</t>
+  </si>
+  <si>
+    <t>0.0006,0.0234,0.9966,0.0011</t>
+  </si>
+  <si>
+    <t>0.0058,0.0002,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.0010,0.9953,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0137,0.9976,0.0013</t>
+  </si>
+  <si>
+    <t>0.0279,0.0434,0.9647,0.0074</t>
+  </si>
+  <si>
+    <t>0.0100,0.0103,0.9703,0.0110</t>
+  </si>
+  <si>
+    <t>0.9785,0.0012,0.0317,0.0009</t>
+  </si>
+  <si>
+    <t>0.8425,0.0009,0.1648,0.0068</t>
+  </si>
+  <si>
+    <t>0.9726,0.0013,0.0384,0.0008</t>
+  </si>
+  <si>
+    <t>0.9948,0.0028,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9976,0.0011,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0018,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9974,0.0012,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9942,0.0026,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0097,0.0056,0.9879,0.0006</t>
+  </si>
+  <si>
+    <t>0.0046,0.0039,0.9946,0.0005</t>
+  </si>
+  <si>
+    <t>0.0189,0.0145,0.9761,0.0024</t>
+  </si>
+  <si>
+    <t>0.0201,0.0107,0.9623,0.0093</t>
+  </si>
+  <si>
+    <t>0.0086,0.0008,0.9942,0.0002</t>
+  </si>
+  <si>
+    <t>0.1347,0.0178,0.8787,0.0115</t>
+  </si>
+  <si>
+    <t>0.4331,0.0050,0.6327,0.0122</t>
+  </si>
+  <si>
+    <t>0.2564,0.0012,0.8128,0.0042</t>
+  </si>
+  <si>
+    <t>0.7228,0.0006,0.0003,0.5762</t>
+  </si>
+  <si>
+    <t>0.0105,0.0028,0.0067,0.9904</t>
+  </si>
+  <si>
+    <t>0.0930,0.0005,0.0007,0.9766</t>
+  </si>
+  <si>
+    <t>0.0066,0.0000,0.0001,0.9985</t>
+  </si>
+  <si>
+    <t>0.0036,0.0023,0.0005,0.9980</t>
+  </si>
+  <si>
+    <t>0.9763,0.0035,0.0036,0.0086</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
